--- a/src/attributions/attributions_saliency_traj_221.xlsx
+++ b/src/attributions/attributions_saliency_traj_221.xlsx
@@ -1568,2278 +1568,2278 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.2419874966144562</v>
+        <v>0.0006009997450746596</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3175024092197418</v>
+        <v>0.001065297285094857</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4312367141246796</v>
+        <v>0.001080783549696207</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05816847831010818</v>
+        <v>0.002013559220358729</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4692943692207336</v>
+        <v>0.001479677390307188</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1272314488887787</v>
+        <v>0.002079293830320239</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1774743497371674</v>
+        <v>0.0008306058589369059</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0793449655175209</v>
+        <v>0.001111468533053994</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01454154774546623</v>
+        <v>0.0002792297163978219</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1231961101293564</v>
+        <v>0.001140989363193512</v>
       </c>
       <c r="K3" t="n">
-        <v>0.252052366733551</v>
+        <v>0.002027595182880759</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3032116889953613</v>
+        <v>0.001413149060681462</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0480964332818985</v>
+        <v>0.001554201473481953</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4561633467674255</v>
+        <v>0.00223978329449892</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0628422349691391</v>
+        <v>0.00131825334392488</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1700263470411301</v>
+        <v>0.002058601472526789</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1805139034986496</v>
+        <v>0.001158689265139401</v>
       </c>
       <c r="R3" t="n">
-        <v>0.06224750727415085</v>
+        <v>0.0005096324603073299</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01373520214110613</v>
+        <v>0.0001195098011521623</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1137356981635094</v>
+        <v>0.000491934479214251</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09510784596204758</v>
+        <v>0.00023726696963422</v>
       </c>
       <c r="V3" t="n">
-        <v>0.06842254102230072</v>
+        <v>5.166771006770432e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1036206856369972</v>
+        <v>0.0004193369532003999</v>
       </c>
       <c r="X3" t="n">
-        <v>0.007811346556991339</v>
+        <v>0.0007924840901978314</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001788591034710407</v>
+        <v>0.0001476532488595694</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.05465508997440338</v>
+        <v>0.0004336664278525859</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.03754644095897675</v>
+        <v>0.0007473455625586212</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.027369175106287</v>
+        <v>0.0002641525061335415</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.04697010666131973</v>
+        <v>0.001120608299970627</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.04384022951126099</v>
+        <v>0.001045529497787356</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.148855909705162</v>
+        <v>0.0005164106842130423</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.115091547369957</v>
+        <v>0.0001869792467914522</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.09690546989440918</v>
+        <v>0.0001590776082593948</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.01669390499591827</v>
+        <v>0.0001765125925885513</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.02879108302295208</v>
+        <v>0.001977018779143691</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.02755728736519814</v>
+        <v>0.001332599436864257</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.008985064923763275</v>
+        <v>0.000551298726350069</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1506858021020889</v>
+        <v>0.001264724647626281</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.06659192591905594</v>
+        <v>0.0004895851598121226</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.01266211643815041</v>
+        <v>0.0006559312460012734</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.07068351656198502</v>
+        <v>0.001857351744547486</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.002887518843635917</v>
+        <v>0.0009216805920004845</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.02968334034085274</v>
+        <v>0.0006758153904229403</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.0281120091676712</v>
+        <v>0.0003998937318101525</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.003271305002272129</v>
+        <v>0.0003053743857890368</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.02961619198322296</v>
+        <v>0.0008942900458350778</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.08102496713399887</v>
+        <v>0.002252299105748534</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.2730127573013306</v>
+        <v>0.0006422671722248197</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.00995283666998148</v>
+        <v>0.000993965077213943</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.4732679426670074</v>
+        <v>0.0005953189684078097</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0891556590795517</v>
+        <v>0.0009312396869063377</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.01613960973918438</v>
+        <v>0.0005394770414568484</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.1939316689968109</v>
+        <v>0.001860829070210457</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.03975377604365349</v>
+        <v>5.756381142418832e-05</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.1710061430931091</v>
+        <v>0.0005068639293313026</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.2406853139400482</v>
+        <v>0.001065311720594764</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.03760176151990891</v>
+        <v>0.0003499182057566941</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.2250770628452301</v>
+        <v>0.0002064746513497084</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.2936468422412872</v>
+        <v>0.002447008620947599</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.2111667692661285</v>
+        <v>0.0002459665993228555</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.01300744526088238</v>
+        <v>0.0002605252666398883</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.2467895150184631</v>
+        <v>0.001278765499591827</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.1560968607664108</v>
+        <v>0.0005363361560739577</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.142820730805397</v>
+        <v>0.0001434432051610202</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.06597904860973358</v>
+        <v>0.0003318999661132693</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.03524661809206009</v>
+        <v>5.454084748635069e-05</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.2075847089290619</v>
+        <v>0.0005497882957570255</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.2387544512748718</v>
+        <v>0.0006439335411414504</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.02070414088666439</v>
+        <v>0.000481544848298654</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.04836613684892654</v>
+        <v>0.0001914814201882109</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.1111690625548363</v>
+        <v>0.0006138674798421562</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.01435155607759953</v>
+        <v>0.0006543584167957306</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.01281863451004028</v>
+        <v>3.753711644094437e-05</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.02086400240659714</v>
+        <v>0.001272145309485495</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.1182455122470856</v>
+        <v>9.102177136810496e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.09672792255878448</v>
+        <v>0.0003016168484464288</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.2186241447925568</v>
+        <v>0.001433953526429832</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.03851216286420822</v>
+        <v>0.0001375655265292153</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.03848845511674881</v>
+        <v>0.0004495773464441299</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.1772910803556442</v>
+        <v>0.0002031988406088203</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.1449422985315323</v>
+        <v>0.001170821604318917</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.006760457996279001</v>
+        <v>0.0002701803168747574</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.01855374872684479</v>
+        <v>0.0004557601641863585</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.09111443161964417</v>
+        <v>0.0003308861050754786</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.02876472473144531</v>
+        <v>0.0001804736966732889</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.09647747129201889</v>
+        <v>0.0002011922042584047</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.004403919912874699</v>
+        <v>0.0006720668752677739</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.01502687111496925</v>
+        <v>0.0001353057741653174</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.0002775304019451141</v>
+        <v>0.0002585708862170577</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.02862193435430527</v>
+        <v>0.0001434347068425268</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.09076074510812759</v>
+        <v>0.000240766181377694</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.1555012166500092</v>
+        <v>0.001218780176714063</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.1180729493498802</v>
+        <v>0.0003710906603373587</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.2046739310026169</v>
+        <v>0.00152475165668875</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.3624886274337769</v>
+        <v>0.00013424624921754</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.06792280822992325</v>
+        <v>0.000102030171547085</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.1762500554323196</v>
+        <v>0.000197473811567761</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.08585122227668762</v>
+        <v>0.0008669036906212568</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.05878377333283424</v>
+        <v>0.0003391497011762112</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.01996838301420212</v>
+        <v>0.0001555154303787276</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.02201245538890362</v>
+        <v>0.0002645190106704831</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.06672448664903641</v>
+        <v>0.0002509342739358544</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.05490929260849953</v>
+        <v>0.0001586548751220107</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.06505993008613586</v>
+        <v>8.106834138743579e-05</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.001450427807867527</v>
+        <v>0.0008548045880161226</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.01835458911955357</v>
+        <v>3.525485226418823e-05</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.004650712478905916</v>
+        <v>0.000433202541898936</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.03904807567596436</v>
+        <v>0.0002436861686874181</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.2355527579784393</v>
+        <v>0.0006072331452742219</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.2027574628591537</v>
+        <v>0.0006643799715675414</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.1467201560735703</v>
+        <v>0.0006994527648203075</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.1761052459478378</v>
+        <v>0.001004599151201546</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.03908813372254372</v>
+        <v>0.00194441294297576</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.2285185307264328</v>
+        <v>0.001833353657275438</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.07757335901260376</v>
+        <v>0.0004389275563880801</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.07319269329309464</v>
+        <v>0.00150440726429224</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.01542307808995247</v>
+        <v>0.00156970345415175</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.08093360066413879</v>
+        <v>0.0009375828667543828</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.07168982923030853</v>
+        <v>0.0002215551357949153</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.08849644660949707</v>
+        <v>0.0003522894694469869</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.003859838470816612</v>
+        <v>3.604614175856113e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.1388249397277832</v>
+        <v>0.000919305719435215</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.07930156588554382</v>
+        <v>0.0004415821167640388</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.0844389796257019</v>
+        <v>0.0005819342331960797</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.104078397154808</v>
+        <v>0.001077589113265276</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.06398724019527435</v>
+        <v>0.0005242134211584926</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.03256281092762947</v>
+        <v>0.0008144347812049091</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.02899969555437565</v>
+        <v>0.0007766721537336707</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.05313242971897125</v>
+        <v>0.0003721453249454498</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.1293906569480896</v>
+        <v>0.000380149605916813</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.03726445138454437</v>
+        <v>0.001590473344549537</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.03933241590857506</v>
+        <v>0.001661519170738757</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.07052126526832581</v>
+        <v>0.0002983632730320096</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.001237500458955765</v>
+        <v>0.001375339226797223</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.1023423224687576</v>
+        <v>0.0002179861621698365</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.0414726659655571</v>
+        <v>0.0005798860220238566</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.05973868817090988</v>
+        <v>0.0003364810545463115</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.1498475223779678</v>
+        <v>0.0001080582151189446</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.140850231051445</v>
+        <v>0.0003827798063866794</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.04406923800706863</v>
+        <v>0.0005722269415855408</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.04106177389621735</v>
+        <v>0.0003671549202408642</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.03566734865307808</v>
+        <v>0.0002062077255686745</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.03108387626707554</v>
+        <v>0.0004534763575065881</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.001048570848070085</v>
+        <v>0.0003911074600182474</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.101195715367794</v>
+        <v>0.0002799216017592698</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.005969678051769733</v>
+        <v>0.0003453494282439351</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.005060820840299129</v>
+        <v>8.984997111838311e-05</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.04535339027643204</v>
+        <v>4.379008532851003e-05</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.1048769503831863</v>
+        <v>0.000181425828486681</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.01520348619669676</v>
+        <v>0.0003606934915296733</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.01318739354610443</v>
+        <v>0.0002989322238136083</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.01565404236316681</v>
+        <v>0.0005034864298067987</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.06585537642240524</v>
+        <v>0.001283246325328946</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.01922998577356339</v>
+        <v>0.0002203093317802995</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.002706458326429129</v>
+        <v>0.0006033924291841686</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.06901400536298752</v>
+        <v>0.0003253684262745082</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.01709022372961044</v>
+        <v>0.000155756002641283</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.07556340098381042</v>
+        <v>5.337700713425875e-06</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.01780929043889046</v>
+        <v>0.0006794139044359326</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.004123513586819172</v>
+        <v>0.0001536534109618515</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.01950329542160034</v>
+        <v>0.0005245720385573804</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.01832619681954384</v>
+        <v>0.0004009369877167046</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.06887118518352509</v>
+        <v>0.0002533339720685035</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.01371497288346291</v>
+        <v>5.524597145267762e-05</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.01688976772129536</v>
+        <v>0.0006845631869509816</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.1227325201034546</v>
+        <v>0.0003796150558628142</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.0527186281979084</v>
+        <v>0.001090083504095674</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.04266133531928062</v>
+        <v>1.845435508585069e-05</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.102964386343956</v>
+        <v>8.854069164954126e-05</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.04288739711046219</v>
+        <v>3.711284080054611e-06</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.04238808900117874</v>
+        <v>0.0009109479724429548</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.04886918887495995</v>
+        <v>0.0001907400146592408</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.1036126315593719</v>
+        <v>0.0007650606567040086</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.00523848831653595</v>
+        <v>0.000501140602864325</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.01262808963656425</v>
+        <v>0.0001449787378078327</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.08076124638319016</v>
+        <v>0.002143941586837173</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.02085557207465172</v>
+        <v>0.001885957084596157</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.05384822189807892</v>
+        <v>0.0004300331347621977</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.2166218310594559</v>
+        <v>0.0001002405188046396</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.04348264262080193</v>
+        <v>0.0005094525404274464</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.01895125582814217</v>
+        <v>0.0002520094567444175</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.1930986791849136</v>
+        <v>0.0002790801227092743</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.04472805932164192</v>
+        <v>0.000310033094137907</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.06945891678333282</v>
+        <v>0.001067058998160064</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.0887434333562851</v>
+        <v>0.0002149281499441713</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.05463756620883942</v>
+        <v>0.0005648244405165315</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.02626324817538261</v>
+        <v>0.0002949557092506438</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.1118650510907173</v>
+        <v>0.001112770987674594</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.008870728313922882</v>
+        <v>0.0001822659542085603</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.01685184985399246</v>
+        <v>0.2885208129882812</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3225304484367371</v>
+        <v>0.5642580986022949</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06026396155357361</v>
+        <v>0.1312312483787537</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1289309710264206</v>
+        <v>0.1201896667480469</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3716041445732117</v>
+        <v>0.1505484879016876</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06747362017631531</v>
+        <v>0.4668028950691223</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1638311296701431</v>
+        <v>0.07867180556058884</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1130078136920929</v>
+        <v>0.3350164592266083</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01136450655758381</v>
+        <v>0.07118342816829681</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06072391197085381</v>
+        <v>0.3347042500972748</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2116725444793701</v>
+        <v>0.536561131477356</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0284684132784605</v>
+        <v>0.2220958322286606</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02003432437777519</v>
+        <v>0.2433059215545654</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3165924847126007</v>
+        <v>0.3271870315074921</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06899277865886688</v>
+        <v>0.3627670109272003</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1577488929033279</v>
+        <v>0.1907243579626083</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02641192637383938</v>
+        <v>0.3082662522792816</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01147108804434538</v>
+        <v>0.2104375958442688</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01932864263653755</v>
+        <v>0.01672610454261303</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05279630795121193</v>
+        <v>0.02869743853807449</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03320562466979027</v>
+        <v>0.07945449650287628</v>
       </c>
       <c r="V4" t="n">
-        <v>0.07179581373929977</v>
+        <v>0.05532937869429588</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1352165788412094</v>
+        <v>0.01075484789907932</v>
       </c>
       <c r="X4" t="n">
-        <v>0.07033582776784897</v>
+        <v>0.07210329174995422</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.04803266748785973</v>
+        <v>0.0007576756179332733</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03037852235138416</v>
+        <v>0.1300903260707855</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001367766410112381</v>
+        <v>0.08253787457942963</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.04179259389638901</v>
+        <v>0.07098634541034698</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.02525912784039974</v>
+        <v>0.2295390069484711</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0005872966721653938</v>
+        <v>0.030002161860466</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.04710710793733597</v>
+        <v>0.05878256261348724</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.03026901558041573</v>
+        <v>0.02364116534590721</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.02918775007128716</v>
+        <v>0.04964154958724976</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.04207653924822807</v>
+        <v>0.002916077151894569</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.02109715901315212</v>
+        <v>0.01769360154867172</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.02291867323219776</v>
+        <v>0.03358979523181915</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.03116827458143234</v>
+        <v>0.0728413462638855</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.09839817136526108</v>
+        <v>0.1862524300813675</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.02189290523529053</v>
+        <v>0.1927198320627213</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.03331858292222023</v>
+        <v>0.09461146593093872</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.02298347093164921</v>
+        <v>0.1473574489355087</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.05997204780578613</v>
+        <v>0.02608760632574558</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.03168043494224548</v>
+        <v>0.03871709853410721</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.03871405869722366</v>
+        <v>0.09455248713493347</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.002941550686955452</v>
+        <v>0.04262582585215569</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.01624683476984501</v>
+        <v>0.1746624410152435</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.2402889728546143</v>
+        <v>0.25291508436203</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.06003652513027191</v>
+        <v>0.1299090832471848</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.06830567866563797</v>
+        <v>0.1358873695135117</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.2044351100921631</v>
+        <v>0.3107312917709351</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.05825157836079597</v>
+        <v>0.1870492696762085</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.007611773442476988</v>
+        <v>0.04605568200349808</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.03913501277565956</v>
+        <v>0.009931609965860844</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.02260592393577099</v>
+        <v>0.0003706607967615128</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.02413654886186123</v>
+        <v>0.00522663863375783</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.04617760702967644</v>
+        <v>0.1191420629620552</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.01735063642263412</v>
+        <v>0.1434848010540009</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.004305491223931313</v>
+        <v>0.00807742215692997</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.1552920937538147</v>
+        <v>0.06170753762125969</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.02333812043070793</v>
+        <v>0.202770859003067</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.07006271928548813</v>
+        <v>0.02348341420292854</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.001442359760403633</v>
+        <v>0.05891789123415947</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.0009508989751338959</v>
+        <v>0.06760759651660919</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.07992220669984818</v>
+        <v>0.05692357569932938</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.02415809594094753</v>
+        <v>0.01633833721280098</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.01108353026211262</v>
+        <v>0.01861031353473663</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.04363453015685081</v>
+        <v>0.03912032395601273</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.02498443797230721</v>
+        <v>0.03309725597500801</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.03968736901879311</v>
+        <v>0.02859247848391533</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.01582879573106766</v>
+        <v>0.07606909424066544</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.02920099720358849</v>
+        <v>0.05715940147638321</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.005201745312660933</v>
+        <v>0.01599962264299393</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.04377039521932602</v>
+        <v>0.1053188890218735</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1844283938407898</v>
+        <v>0.1564102470874786</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.03069517388939857</v>
+        <v>0.1037656739354134</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.04815018549561501</v>
+        <v>0.09937292337417603</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.1784005463123322</v>
+        <v>0.07451089471578598</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.1198418885469437</v>
+        <v>0.1331381350755692</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.04305370524525642</v>
+        <v>0.05903737246990204</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.01781027391552925</v>
+        <v>0.09296411275863647</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.01040850207209587</v>
+        <v>0.05535214766860008</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.02354498952627182</v>
+        <v>0.05743970721960068</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.03333641216158867</v>
+        <v>0.2021483182907104</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.01984863169491291</v>
+        <v>0.01208788808435202</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.02696945518255234</v>
+        <v>0.05273592844605446</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.05506346002221107</v>
+        <v>0.01732048578560352</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.04806113615632057</v>
+        <v>0.1319843679666519</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.005528461188077927</v>
+        <v>0.0337122455239296</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.01201316900551319</v>
+        <v>0.08187830448150635</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.0138519536703825</v>
+        <v>0.03700130805373192</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.0211312472820282</v>
+        <v>0.06194910407066345</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0246626827865839</v>
+        <v>0.2555920779705048</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.01387666538357735</v>
+        <v>0.156315952539444</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.04942887648940086</v>
+        <v>0.1673954576253891</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.0725397989153862</v>
+        <v>0.01748065650463104</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.009042234160006046</v>
+        <v>0.08847051858901978</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.09359645843505859</v>
+        <v>0.007322291843593121</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.09050349146127701</v>
+        <v>0.004083461128175259</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.01377031486481428</v>
+        <v>0.07638052850961685</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.02441686764359474</v>
+        <v>0.06101161986589432</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.01951408386230469</v>
+        <v>0.1908822655677795</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.01785886101424694</v>
+        <v>0.004202520474791527</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.03310329094529152</v>
+        <v>0.06128518655896187</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.05695107579231262</v>
+        <v>0.01333598420023918</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.07282555848360062</v>
+        <v>0.1259942054748535</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.008023696951568127</v>
+        <v>0.04195012524724007</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.006371136754751205</v>
+        <v>0.1041039898991585</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.003733045421540737</v>
+        <v>0.02071885578334332</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.02456508204340935</v>
+        <v>0.007785710040479898</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.1034613475203514</v>
+        <v>0.1379833370447159</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.01993395946919918</v>
+        <v>0.054073765873909</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.1148405000567436</v>
+        <v>0.09229973703622818</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.01187849603593349</v>
+        <v>0.07733998447656631</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.02790631353855133</v>
+        <v>0.2173332571983337</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.1074088662862778</v>
+        <v>0.06493331491947174</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.02941249497234821</v>
+        <v>0.1463596522808075</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.01389073953032494</v>
+        <v>0.142504408955574</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.06692437827587128</v>
+        <v>0.01068210229277611</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.04770239815115929</v>
+        <v>0.1213680729269981</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.0629202127456665</v>
+        <v>0.05307917669415474</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0841389000415802</v>
+        <v>0.08006402105093002</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.02954640053212643</v>
+        <v>0.0134938471019268</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.01898430846631527</v>
+        <v>0.1131895631551743</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.001458598300814629</v>
+        <v>0.01427129935473204</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.08742819726467133</v>
+        <v>0.07684605568647385</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.01619182527065277</v>
+        <v>0.06614553183317184</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.003071912098675966</v>
+        <v>0.05928856134414673</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.05093097686767578</v>
+        <v>0.05700157955288887</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.03398137539625168</v>
+        <v>0.1395858228206635</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0113099692389369</v>
+        <v>0.1073253303766251</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.08071279525756836</v>
+        <v>0.2101233899593353</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.01551257725805044</v>
+        <v>0.2462712675333023</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.0006053997203707695</v>
+        <v>0.08321569859981537</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.02871899120509624</v>
+        <v>0.1741753816604614</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.03636392205953598</v>
+        <v>0.1718897968530655</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.02007152512669563</v>
+        <v>0.009796245023608208</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.01058132667094469</v>
+        <v>0.1114389449357986</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.006180757191032171</v>
+        <v>0.1320159435272217</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.007697691675275564</v>
+        <v>0.02670919336378574</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.06352329254150391</v>
+        <v>0.005001243203878403</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.04692155122756958</v>
+        <v>0.1403423696756363</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.01439467445015907</v>
+        <v>0.004530759993940592</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0109820906072855</v>
+        <v>0.05892226099967957</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.009486589580774307</v>
+        <v>0.06744282692670822</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.01190989185124636</v>
+        <v>0.07540196925401688</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.03019812703132629</v>
+        <v>0.1304536759853363</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.004350076429545879</v>
+        <v>0.08279481530189514</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.003815991804003716</v>
+        <v>0.04479172453284264</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.001513409893959761</v>
+        <v>0.0697738379240036</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.2110254913568497</v>
+        <v>0.03189945966005325</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.006547960918396711</v>
+        <v>0.01496817357838154</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.07693216949701309</v>
+        <v>0.09026944637298584</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.03502422571182251</v>
+        <v>0.125620111823082</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0271914079785347</v>
+        <v>0.06254050880670547</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.008995683863759041</v>
+        <v>0.2357662618160248</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.02585525624454021</v>
+        <v>0.001407302683219314</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.03893575072288513</v>
+        <v>0.07164963334798813</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.06138391047716141</v>
+        <v>0.01048517599701881</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.05608092993497849</v>
+        <v>0.09563634544610977</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.005932576023042202</v>
+        <v>0.02305435016751289</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.01553716231137514</v>
+        <v>0.1272837817668915</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.001384691800922155</v>
+        <v>0.001466775313019753</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.02851181104779243</v>
+        <v>0.01290731690824032</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.06700659543275833</v>
+        <v>0.1518027782440186</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.01119966991245747</v>
+        <v>0.03057128190994263</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.05779164656996727</v>
+        <v>0.07279900461435318</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.002814237028360367</v>
+        <v>0.1178320124745369</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.0485951229929924</v>
+        <v>0.07519824802875519</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.001485452055931091</v>
+        <v>0.1143542677164078</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.01673902198672295</v>
+        <v>0.1366559863090515</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.02240478619933128</v>
+        <v>0.03469271957874298</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.02233773842453957</v>
+        <v>0.09838441014289856</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.06839756667613983</v>
+        <v>0.3112358450889587</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.04688031226396561</v>
+        <v>0.3395589292049408</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.04038337618112564</v>
+        <v>0.1304877549409866</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.1519271731376648</v>
+        <v>0.09350255131721497</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.02023418247699738</v>
+        <v>0.08301337063312531</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.04348175227642059</v>
+        <v>0.1711571216583252</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.04727455973625183</v>
+        <v>0.08105406910181046</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.02665799111127853</v>
+        <v>0.08506986498832703</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.03502035140991211</v>
+        <v>0.1154428645968437</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.014599634334445</v>
+        <v>0.01977049559354782</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.06268990039825439</v>
+        <v>0.05630361288785934</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.04199064522981644</v>
+        <v>0.03257087245583534</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.09066049754619598</v>
+        <v>0.06830596178770065</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.0357036255300045</v>
+        <v>0.04924483597278595</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.1007775887846947</v>
+        <v>0.01157907024025917</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.005875503644347191</v>
+        <v>0.1450182348489761</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.01495830714702606</v>
+        <v>0.1571331173181534</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0001386082731187344</v>
+        <v>0.004014092963188887</v>
       </c>
       <c r="B5" t="n">
-        <v>0.003720554290339351</v>
+        <v>0.04411591216921806</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002309995034011081</v>
+        <v>0.02495519816875458</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001910562277771533</v>
+        <v>0.01020452007651329</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002091638743877411</v>
+        <v>0.005621539428830147</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001418681349605322</v>
+        <v>0.02099454030394554</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0005357424379326403</v>
+        <v>0.0001570750027894974</v>
       </c>
       <c r="H5" t="n">
-        <v>6.476366252172738e-05</v>
+        <v>0.003344167256727815</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003152618883177638</v>
+        <v>0.01553444750607014</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000109918080852367</v>
+        <v>0.0003931256360374391</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003178672399371862</v>
+        <v>0.04552195221185684</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002937218232546002</v>
+        <v>0.02971511892974377</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003805970191024244</v>
+        <v>0.01864480040967464</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001271143322810531</v>
+        <v>0.0001720551081234589</v>
       </c>
       <c r="O5" t="n">
-        <v>0.000816843647044152</v>
+        <v>0.01085358299314976</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00095962273189798</v>
+        <v>0.002250341698527336</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0007132311584427953</v>
+        <v>0.0121593251824379</v>
       </c>
       <c r="R5" t="n">
-        <v>4.631874617189169e-05</v>
+        <v>0.009309234097599983</v>
       </c>
       <c r="S5" t="n">
-        <v>8.482608973281458e-05</v>
+        <v>0.002919060876592994</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0001819163735490292</v>
+        <v>0.006532575003802776</v>
       </c>
       <c r="U5" t="n">
-        <v>2.885804860852659e-05</v>
+        <v>0.01314151752740145</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0006039673462510109</v>
+        <v>0.001406712108291686</v>
       </c>
       <c r="W5" t="n">
-        <v>3.253028626204468e-05</v>
+        <v>0.001145096146501601</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002733087749220431</v>
+        <v>0.01358054205775261</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0004428486863616854</v>
+        <v>0.001383217866532505</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0001901411305880174</v>
+        <v>0.0002051360788755119</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0005474661593325436</v>
+        <v>0.00790389534085989</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.979400783777237e-05</v>
+        <v>0.00689777871593833</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.224543615942821e-05</v>
+        <v>0.009015647694468498</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0004701527068391442</v>
+        <v>0.001204090192914009</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0007679859991185367</v>
+        <v>0.01673748344182968</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0003877205890603364</v>
+        <v>0.01551895774900913</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0003795515222009271</v>
+        <v>0.003414034377783537</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.288471634732559e-05</v>
+        <v>0.008141430094838142</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0006001172005198896</v>
+        <v>0.00344438711181283</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.000404618593165651</v>
+        <v>0.005795245058834553</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0001821512851165608</v>
+        <v>0.001078937901183963</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0006157727912068367</v>
+        <v>0.009659081697463989</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.000238530890783295</v>
+        <v>0.009231844916939735</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.996353037422523e-05</v>
+        <v>0.007446779403835535</v>
       </c>
       <c r="AO5" t="n">
-        <v>3.672441744129173e-05</v>
+        <v>0.01757039502263069</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.0004340341547504067</v>
+        <v>0.00851159356534481</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0001194404612760991</v>
+        <v>0.004749291110783815</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.000342138868290931</v>
+        <v>0.001098435954190791</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.0003383731527719647</v>
+        <v>0.0008886970463208854</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0005038776434957981</v>
+        <v>0.001575538888573647</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.001884965924546123</v>
+        <v>0.0345587320625782</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.97952356049791e-05</v>
+        <v>0.003666400443762541</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.001807984081096947</v>
+        <v>0.01298380363732576</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.001456532976590097</v>
+        <v>0.001663043280132115</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.0008184247999452055</v>
+        <v>0.007826809771358967</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0006901276065036654</v>
+        <v>0.0009301831014454365</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0002868784358724952</v>
+        <v>0.003742025699466467</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.0007321796729229391</v>
+        <v>0.005077917594462633</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0004185512661933899</v>
+        <v>0.006591788958758116</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0005756508908234537</v>
+        <v>0.005118462257087231</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.0005289760301820934</v>
+        <v>0.01291711535304785</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.259151268750429e-05</v>
+        <v>0.007264007814228535</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.001166684320196509</v>
+        <v>0.004636500030755997</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.000474061060231179</v>
+        <v>0.01684600673615932</v>
       </c>
       <c r="BI5" t="n">
-        <v>8.709060784894973e-05</v>
+        <v>0.003068801481276751</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.000787838245742023</v>
+        <v>0.003363695926964283</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0003273831389378756</v>
+        <v>0.009455903433263302</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0001437092723790556</v>
+        <v>0.003289763350039721</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0003787893801927567</v>
+        <v>0.006940980441868305</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.0002608980285003781</v>
+        <v>0.006021793931722641</v>
       </c>
       <c r="BO5" t="n">
-        <v>6.808697071392089e-05</v>
+        <v>0.01019216887652874</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0009475864935666323</v>
+        <v>0.002235951367765665</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0002088538749376312</v>
+        <v>0.0003842037112917751</v>
       </c>
       <c r="BR5" t="n">
-        <v>5.747249451815151e-05</v>
+        <v>0.003743584267795086</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.0005717500462196767</v>
+        <v>0.003216065466403961</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.271926395129412e-05</v>
+        <v>0.002991406247019768</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0004669974441640079</v>
+        <v>0.003130587516352534</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.001307661063037813</v>
+        <v>0.02221422456204891</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.043092045933008e-05</v>
+        <v>0.0016853844281286</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.0006796065717935562</v>
+        <v>0.006488843820989132</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.0006320350803434849</v>
+        <v>0.003204561537131667</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.000173745458596386</v>
+        <v>0.01561240013688803</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.0003769708564504981</v>
+        <v>0.0004024067893624306</v>
       </c>
       <c r="CB5" t="n">
-        <v>9.052166569745168e-05</v>
+        <v>0.001450990908779204</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.0005026119761168957</v>
+        <v>0.009099963121116161</v>
       </c>
       <c r="CD5" t="n">
-        <v>9.601779311196879e-05</v>
+        <v>0.0008671333780512214</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.0003913495747838169</v>
+        <v>0.01480087824165821</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0001933717867359519</v>
+        <v>0.01064473111182451</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0003910056839231402</v>
+        <v>0.005818618461489677</v>
       </c>
       <c r="CH5" t="n">
-        <v>4.445565718924627e-05</v>
+        <v>0.0004215155786368996</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0002261541085317731</v>
+        <v>0.001025581383146346</v>
       </c>
       <c r="CJ5" t="n">
-        <v>5.47540548723191e-06</v>
+        <v>0.0002267765230499208</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.0001196681478177197</v>
+        <v>0.0008627648930996656</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.000410142878536135</v>
+        <v>0.00406725937500596</v>
       </c>
       <c r="CM5" t="n">
-        <v>3.042619391635526e-05</v>
+        <v>0.004509192425757647</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0005067542078904808</v>
+        <v>0.01232200488448143</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.0001670529745751992</v>
+        <v>0.004699671640992165</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.0007833045674487948</v>
+        <v>0.01428071968257427</v>
       </c>
       <c r="CQ5" t="n">
-        <v>7.724772149231285e-05</v>
+        <v>0.005509800277650356</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.000823642301838845</v>
+        <v>0.013042276725173</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.001030551851727068</v>
+        <v>0.00324687035754323</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0004742545424960554</v>
+        <v>0.001078549074009061</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0001690234494162723</v>
+        <v>0.006328847259283066</v>
       </c>
       <c r="CV5" t="n">
-        <v>7.321206794586033e-06</v>
+        <v>0.001318287802860141</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.0004843796486966312</v>
+        <v>0.01503897644579411</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0002490436600055546</v>
+        <v>0.01117153000086546</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0005489119794219732</v>
+        <v>0.005293709225952625</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0001476260367780924</v>
+        <v>0.001249375403858721</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0003798906109295785</v>
+        <v>0.0004529768484644592</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0001232583599630743</v>
+        <v>0.0007851053960621357</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0001874707377282903</v>
+        <v>0.0002869685995392501</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.0003605942474678159</v>
+        <v>0.005450570024549961</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.000144805817399174</v>
+        <v>0.007252853363752365</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.000696835748385638</v>
+        <v>0.02394966222345829</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0004336155543569475</v>
+        <v>0.0178841594606638</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.002453195163980126</v>
+        <v>0.0113193616271019</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.001740113599225879</v>
+        <v>0.005543442908674479</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.0001377367880195379</v>
+        <v>0.0005026478320360184</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.0009296572534367442</v>
+        <v>0.003613083390519023</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.001216516364365816</v>
+        <v>0.009619760327041149</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0002158032439183444</v>
+        <v>0.009011249989271164</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.000399493204895407</v>
+        <v>0.00151461863424629</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0003582770295906812</v>
+        <v>0.003955114632844925</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.0008899194654077291</v>
+        <v>0.005586727522313595</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0002176416455768049</v>
+        <v>0.001932383631356061</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.0002054366923402995</v>
+        <v>0.004414593800902367</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.0002903505810536444</v>
+        <v>0.008348152041435242</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.0001815177965909243</v>
+        <v>0.0005074178334325552</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0003016275004483759</v>
+        <v>0.0008806306286714971</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.0004862102796323597</v>
+        <v>0.009670184925198555</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0002096005191560835</v>
+        <v>0.002804675372317433</v>
       </c>
       <c r="DX5" t="n">
-        <v>5.055231304140761e-05</v>
+        <v>0.007845936343073845</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0007111962768249214</v>
+        <v>0.008995477110147476</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0003930603561457247</v>
+        <v>0.005827607121318579</v>
       </c>
       <c r="EA5" t="n">
-        <v>2.887215850932989e-05</v>
+        <v>0.01210261601954699</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.0003014734829775989</v>
+        <v>0.006995291449129581</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0001453524164389819</v>
+        <v>0.0004255937528796494</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.0003838241682387888</v>
+        <v>0.006541196256875992</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.0002965763560496271</v>
+        <v>0.006091243121773005</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0003786436282098293</v>
+        <v>0.001114130485802889</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.0003025117330253124</v>
+        <v>0.0147183071821928</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.0004120517696719617</v>
+        <v>0.007153189741075039</v>
       </c>
       <c r="EI5" t="n">
-        <v>3.342660784255713e-05</v>
+        <v>0.004773413762450218</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0005677255103364587</v>
+        <v>0.0009225588291883469</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0004729558131657541</v>
+        <v>0.009073968045413494</v>
       </c>
       <c r="EL5" t="n">
-        <v>7.856142474338412e-07</v>
+        <v>0.001027551828883588</v>
       </c>
       <c r="EM5" t="n">
-        <v>3.004140489792917e-05</v>
+        <v>0.0002777947811409831</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.0001675477833487093</v>
+        <v>0.00512088555842638</v>
       </c>
       <c r="EO5" t="n">
-        <v>7.024961814749986e-05</v>
+        <v>0.001111639547161758</v>
       </c>
       <c r="EP5" t="n">
-        <v>6.339618266792968e-05</v>
+        <v>0.001339969225227833</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.0002432503242744133</v>
+        <v>0.005271150730550289</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0002790083235595375</v>
+        <v>0.0007062489166855812</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0001859673939179629</v>
+        <v>0.0006017136620357633</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.0006140758050605655</v>
+        <v>0.0007789266528561711</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.000254749960731715</v>
+        <v>0.004052897449582815</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.0003856272669509053</v>
+        <v>0.002428412903100252</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.0001777495635906234</v>
+        <v>0.006315167527645826</v>
       </c>
       <c r="EX5" t="n">
-        <v>3.200824357918464e-05</v>
+        <v>0.001712424331344664</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.0004525848489720374</v>
+        <v>0.01587715931236744</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0001021881762426347</v>
+        <v>0.009359433315694332</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.0004439156327862293</v>
+        <v>0.007162559777498245</v>
       </c>
       <c r="FB5" t="n">
-        <v>5.017410512664355e-05</v>
+        <v>0.00228992011398077</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0002409787412034348</v>
+        <v>0.001861372147686779</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0001017020986182615</v>
+        <v>0.0003561361227184534</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.0001114988554036245</v>
+        <v>0.0009039599681273103</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.0004430067201610655</v>
+        <v>0.005031879525631666</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0001061541188391857</v>
+        <v>0.0003936843713745475</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0004920618957839906</v>
+        <v>0.01341167278587818</v>
       </c>
       <c r="FI5" t="n">
-        <v>5.060968760517426e-05</v>
+        <v>0.0007131223101168871</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.0005876041250303388</v>
+        <v>0.004660785663872957</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0003364443255122751</v>
+        <v>0.01097938977181911</v>
       </c>
       <c r="FL5" t="n">
-        <v>8.736518793739378e-05</v>
+        <v>0.004385783802717924</v>
       </c>
       <c r="FM5" t="n">
-        <v>9.467679774388671e-06</v>
+        <v>0.001934843370690942</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.00047828140668571</v>
+        <v>0.002464205026626587</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.0001295647380175069</v>
+        <v>0.01076971739530563</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.0001132145771407522</v>
+        <v>0.0006028632633388042</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0007463008514605463</v>
+        <v>0.01439511403441429</v>
       </c>
       <c r="FR5" t="n">
-        <v>3.508048393996432e-05</v>
+        <v>0.01391248032450676</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.0008675287826918066</v>
+        <v>0.01573267951607704</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.000772991101257503</v>
+        <v>0.001922940602526069</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0002768593840301037</v>
+        <v>0.01151948980987072</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0001991205936064944</v>
+        <v>0.002261087065562606</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.0001147357688751072</v>
+        <v>0.001504719955846667</v>
       </c>
       <c r="FX5" t="n">
-        <v>4.581687971949577e-05</v>
+        <v>0.001164231449365616</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.0001935619511641562</v>
+        <v>0.0116525162011385</v>
       </c>
       <c r="FZ5" t="n">
-        <v>5.071511623100378e-06</v>
+        <v>0.01854153908789158</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.0002117580734193325</v>
+        <v>0.02488045953214169</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.0007534403121098876</v>
+        <v>0.004683493636548519</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.0008082689018920064</v>
+        <v>0.003013588488101959</v>
       </c>
       <c r="GD5" t="n">
-        <v>7.96788590378128e-05</v>
+        <v>0.0070311538875103</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.001118556247092783</v>
+        <v>0.008759923279285431</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.000189085621968843</v>
+        <v>0.004274340812116861</v>
       </c>
       <c r="GG5" t="n">
-        <v>5.462991612148471e-05</v>
+        <v>0.002515934407711029</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.01861057803034782</v>
+        <v>7.691685459576547e-05</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2371256947517395</v>
+        <v>0.0003072718100156635</v>
       </c>
       <c r="C6" t="n">
-        <v>0.006445686332881451</v>
+        <v>8.086328307399526e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1187348589301109</v>
+        <v>0.000139282681629993</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0323340892791748</v>
+        <v>2.964583836728707e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.203238770365715</v>
+        <v>0.0002460949181113392</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001469207927584648</v>
+        <v>7.335331611102447e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.08297643065452576</v>
+        <v>5.382629024097696e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01685802266001701</v>
+        <v>2.620859049784485e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04856201261281967</v>
+        <v>6.06481044087559e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2230824679136276</v>
+        <v>0.0003722988767549396</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004515244159847498</v>
+        <v>3.619294875534251e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>0.08597143739461899</v>
+        <v>0.0002394993061898276</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003100891131907701</v>
+        <v>0.0001041201467160136</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1893228590488434</v>
+        <v>0.0003065447090193629</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01312901824712753</v>
+        <v>1.62144388013985e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03677046671509743</v>
+        <v>5.395979678723961e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>0.005585072096437216</v>
+        <v>5.801376391900703e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01078718341886997</v>
+        <v>2.669899913598783e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01615801453590393</v>
+        <v>3.404895687708631e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02153419330716133</v>
+        <v>3.690987796289846e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03197560459375381</v>
+        <v>3.376134191057645e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0583316832780838</v>
+        <v>1.433596480637789e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0186696108430624</v>
+        <v>4.896780956187285e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01893303729593754</v>
+        <v>3.684147304738872e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.05739665031433105</v>
+        <v>0.0001411184493917972</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03486910462379456</v>
+        <v>8.815244655124843e-06</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001438789069652557</v>
+        <v>6.378634134307504e-05</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0133759044110775</v>
+        <v>3.182239743182436e-05</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.009325931780040264</v>
+        <v>2.891817348427139e-05</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.009861024096608162</v>
+        <v>7.368098886217922e-05</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01389772724360228</v>
+        <v>7.501863001380116e-05</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.0143308974802494</v>
+        <v>9.57558659138158e-05</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.01284622400999069</v>
+        <v>1.038577920553507e-05</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.008509773761034012</v>
+        <v>0.0002094470110023394</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0130384424701333</v>
+        <v>3.103895505773835e-05</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.02094356715679169</v>
+        <v>7.265630119945854e-05</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.04187099635601044</v>
+        <v>3.806336462730542e-05</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.002297541126608849</v>
+        <v>3.82097132387571e-05</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.008399352431297302</v>
+        <v>3.109603494522162e-05</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.0009102043695747852</v>
+        <v>3.698737600643653e-06</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.02807123400270939</v>
+        <v>4.573251771944342e-06</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.00256158341653645</v>
+        <v>3.918401489499956e-05</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.01317024976015091</v>
+        <v>0.000139212075737305</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.02483553253114223</v>
+        <v>2.128598316630814e-05</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.03235190361738205</v>
+        <v>0.0001164827408501878</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1736998409032822</v>
+        <v>0.0002425203565508127</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.005375235341489315</v>
+        <v>6.464351463364437e-05</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.04496053233742714</v>
+        <v>6.902298628119752e-05</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.01709465309977531</v>
+        <v>0.0001876322639873251</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.1077655255794525</v>
+        <v>0.0001726334303384647</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.02394679933786392</v>
+        <v>5.942084499110933e-06</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.0204777829349041</v>
+        <v>8.392642484977841e-06</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.06129929423332214</v>
+        <v>4.703050944954157e-05</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.0216589942574501</v>
+        <v>1.221837555931415e-05</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.03791249915957451</v>
+        <v>5.933384090894833e-05</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.04754414781928062</v>
+        <v>1.650933700148016e-05</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.00249142711982131</v>
+        <v>0.0001169502138509415</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.03823554515838623</v>
+        <v>7.435803854605183e-05</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.06128839775919914</v>
+        <v>5.427400537882932e-05</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.01917595602571964</v>
+        <v>2.736876922426745e-05</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.01999368704855442</v>
+        <v>8.326924580615014e-05</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.01394461281597614</v>
+        <v>5.294046422932297e-05</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.0001503666862845421</v>
+        <v>1.321857234870549e-05</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0546487532556057</v>
+        <v>3.645935066742823e-05</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.00672224722802639</v>
+        <v>1.886590212052397e-06</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.01508929952979088</v>
+        <v>6.962921179365367e-05</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.003939978778362274</v>
+        <v>2.317588041478302e-05</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.001912229578010738</v>
+        <v>1.05286089819856e-05</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.01697306707501411</v>
+        <v>0.000124360216432251</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.006471746601164341</v>
+        <v>1.833459464251064e-05</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.006727925501763821</v>
+        <v>8.065887232078239e-05</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.01539248321205378</v>
+        <v>3.784135333262384e-05</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.09007550776004791</v>
+        <v>0.0001345257624052465</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.01483060978353024</v>
+        <v>2.049492104561068e-05</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.03765137121081352</v>
+        <v>6.383928848663345e-05</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.02255133725702763</v>
+        <v>3.248325811000541e-06</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.04176545515656471</v>
+        <v>8.927455201046541e-05</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.01393814291805029</v>
+        <v>3.400472633074969e-05</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.0002313493750989437</v>
+        <v>2.527182368794456e-05</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.04003608599305153</v>
+        <v>4.524458199739456e-05</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.001381583511829376</v>
+        <v>1.066539516614284e-05</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.03101350367069244</v>
+        <v>9.209743438987061e-05</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.02275220118463039</v>
+        <v>3.784714863286354e-06</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.01631583645939827</v>
+        <v>3.520170139381662e-05</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.005913358181715012</v>
+        <v>1.502861596236471e-05</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.0315823070704937</v>
+        <v>8.074149081949145e-05</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.01641953736543655</v>
+        <v>2.530566962377634e-05</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.01131806336343288</v>
+        <v>1.880705167423002e-05</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.02083336561918259</v>
+        <v>3.772290074266493e-05</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.05034342035651207</v>
+        <v>3.250980807933956e-05</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.007730855606496334</v>
+        <v>9.80980257736519e-05</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.005318635143339634</v>
+        <v>8.703589264769107e-05</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.0362873338162899</v>
+        <v>0.0001225228043040261</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.001192907337099314</v>
+        <v>2.261467670905404e-06</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.006107674911618233</v>
+        <v>8.500288822688162e-05</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.04923717677593231</v>
+        <v>5.848703949595802e-06</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.04619910195469856</v>
+        <v>0.0001025323872454464</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.009500612504780293</v>
+        <v>3.769935574382544e-05</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.0001195187214761972</v>
+        <v>2.348103953409009e-05</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.02730012498795986</v>
+        <v>8.889888704288751e-05</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.01881650649011135</v>
+        <v>1.058936959452694e-06</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.02870979718863964</v>
+        <v>5.380349466577172e-05</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.007997095584869385</v>
+        <v>1.63135991897434e-05</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.03324554488062859</v>
+        <v>8.741121564526111e-05</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.01652374491095543</v>
+        <v>5.449879608931951e-06</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.02352634444832802</v>
+        <v>2.382257298449986e-05</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.01090287044644356</v>
+        <v>3.269608714617789e-05</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.005340783856809139</v>
+        <v>2.506393684598152e-05</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.01120668277144432</v>
+        <v>5.012480323784985e-05</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.007310524582862854</v>
+        <v>4.254374653100967e-05</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.08527781814336777</v>
+        <v>1.193059233628446e-05</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.04483778774738312</v>
+        <v>0.0001924586395034567</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.02795918844640255</v>
+        <v>8.084376895567402e-05</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.004713171161711216</v>
+        <v>5.913638233323582e-05</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.03878370299935341</v>
+        <v>1.742140739224851e-06</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.02164205349981785</v>
+        <v>2.927568857558072e-06</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.004920377396047115</v>
+        <v>3.202759035048075e-05</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.0031406763009727</v>
+        <v>6.178076728247106e-05</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.01693795807659626</v>
+        <v>1.819178214645945e-05</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.0004337313584983349</v>
+        <v>5.311001586960629e-05</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.008421801961958408</v>
+        <v>2.330850657017436e-05</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.002283880952745676</v>
+        <v>2.551390934968367e-05</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.00104664801619947</v>
+        <v>5.983177834423259e-05</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.002834649290889502</v>
+        <v>0.0001228998880833387</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.02057269774377346</v>
+        <v>4.802750481758267e-05</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.0001513669267296791</v>
+        <v>3.133450445602648e-05</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.0252188928425312</v>
+        <v>1.87354235094972e-05</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.01928079500794411</v>
+        <v>3.274233677075244e-05</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.008103316649794579</v>
+        <v>4.372009425424039e-05</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.00138934375718236</v>
+        <v>6.830459460616112e-05</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.01551226247102022</v>
+        <v>4.313945100875571e-05</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.0007104217074811459</v>
+        <v>3.700749584822915e-05</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.004836912266910076</v>
+        <v>6.078441219870001e-05</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.0101972296833992</v>
+        <v>7.395865395665169e-05</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.01348243094980717</v>
+        <v>2.134999022018746e-06</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.03572700917720795</v>
+        <v>2.157592825824395e-05</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.01130735781043768</v>
+        <v>3.755558282136917e-05</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.007187223993241787</v>
+        <v>1.986643837881275e-06</v>
       </c>
       <c r="EJ6" t="n">
-        <v>8.202483877539635e-05</v>
+        <v>1.140911626862362e-05</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.02313658222556114</v>
+        <v>2.899988248827867e-05</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.01592731103301048</v>
+        <v>1.62789237947436e-05</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.006859187036752701</v>
+        <v>6.775162091798848e-06</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.01097701955586672</v>
+        <v>1.743659959174693e-05</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.001153502613306046</v>
+        <v>3.267017018515617e-05</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.01492869574576616</v>
+        <v>4.102702951058745e-05</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.01754457503557205</v>
+        <v>4.007309325970709e-05</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.02199815027415752</v>
+        <v>4.721219738712534e-05</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.01740813255310059</v>
+        <v>4.862611240241677e-05</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.02959133125841618</v>
+        <v>6.817911344114691e-05</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.03905221074819565</v>
+        <v>2.747707912931219e-05</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.06678984314203262</v>
+        <v>4.716587864095345e-05</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.005901198834180832</v>
+        <v>4.893737786915153e-05</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.004123020451515913</v>
+        <v>2.409339685982559e-05</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.02567833662033081</v>
+        <v>0.0001116581843234599</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.0155309671536088</v>
+        <v>1.008548451864044e-06</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.02027012594044209</v>
+        <v>6.7401364503894e-05</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.004942032974213362</v>
+        <v>3.361576091265306e-05</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.02759478241205215</v>
+        <v>6.965905777178705e-05</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.02859637886285782</v>
+        <v>1.932503073476255e-05</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.01527217030525208</v>
+        <v>2.0131274141022e-05</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.02188032492995262</v>
+        <v>1.615869223314803e-05</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.01078008860349655</v>
+        <v>2.069177753583062e-05</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.007210119161754847</v>
+        <v>0.0001290930085815489</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.01567903906106949</v>
+        <v>7.44444114388898e-05</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.03749755769968033</v>
+        <v>9.857016993919387e-05</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.008984709158539772</v>
+        <v>4.490958963287994e-05</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.01825453341007233</v>
+        <v>0.0001205470762215555</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.0005547641776502132</v>
+        <v>1.38623763632495e-05</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.01815658807754517</v>
+        <v>7.851590635254979e-05</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.01698459312319756</v>
+        <v>6.700785888824612e-05</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.01559801958501339</v>
+        <v>1.580220487085171e-05</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.03934814780950546</v>
+        <v>3.913992986781523e-05</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.03251191973686218</v>
+        <v>0.0001950183359440416</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.0003659832291305065</v>
+        <v>3.248353459639475e-05</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.004876871593296528</v>
+        <v>0.0001110694793169387</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.01117378659546375</v>
+        <v>1.0976964404108e-05</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.02655639685690403</v>
+        <v>3.012898014276288e-05</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.004022484645247459</v>
+        <v>2.379688339715358e-05</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.01491651218384504</v>
+        <v>1.347186116618104e-05</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.04654818028211594</v>
+        <v>1.862807766883634e-05</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.01586588658392429</v>
+        <v>6.941500760149211e-05</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.02829737588763237</v>
+        <v>6.398886034730822e-05</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.01245159562677145</v>
+        <v>1.255087590834592e-05</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.01304948329925537</v>
+        <v>0.0001825021317927167</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.01801168918609619</v>
+        <v>8.525674638804048e-05</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.1004845723509789</v>
+        <v>2.506627606635448e-05</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.001938051544129848</v>
+        <v>3.56614327756688e-05</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.004058975260704756</v>
+        <v>2.736289025051519e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4982,1140 +4982,1140 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.000144314777571708</v>
+        <v>9.684785027275211e-07</v>
       </c>
       <c r="B9" t="n">
-        <v>0.001869396190159023</v>
+        <v>5.619906914944295e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001237125543411821</v>
+        <v>4.913781594950706e-07</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000392859656130895</v>
+        <v>1.713130131975049e-06</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0004673385119531304</v>
+        <v>2.78321499536105e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0004175872600171715</v>
+        <v>8.052302291616797e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>0.000289405114017427</v>
+        <v>2.796407898131292e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0002337529003852978</v>
+        <v>5.58515966986306e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002795870532281697</v>
+        <v>5.080403298052261e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002041987463599071</v>
+        <v>5.367971880332334e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001648076227866113</v>
+        <v>6.849195415270515e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>4.456980605027638e-06</v>
+        <v>2.680597390281036e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0002343781525269151</v>
+        <v>4.080195594724501e-06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.928599370643497e-05</v>
+        <v>6.673756161035271e-06</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0003300730313640088</v>
+        <v>1.065810465661343e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0001585933787282556</v>
+        <v>1.781623495844542e-06</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0001919291680678725</v>
+        <v>3.687071966851363e-06</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0003656261833384633</v>
+        <v>1.2646103186853e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>8.659066224936396e-05</v>
+        <v>1.97168361637523e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0002210674429079518</v>
+        <v>4.724053042082232e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>6.789417966501787e-05</v>
+        <v>1.110426183004165e-06</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0001651412167120725</v>
+        <v>6.557239657922764e-07</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0002051943447440863</v>
+        <v>9.018548894346168e-07</v>
       </c>
       <c r="X9" t="n">
-        <v>6.040728112566285e-05</v>
+        <v>1.340832113783108e-06</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.820397821778897e-05</v>
+        <v>8.903189154807478e-07</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0003487916255835444</v>
+        <v>2.789565314742504e-06</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0001241104037035257</v>
+        <v>7.29408384358976e-07</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.000136229646159336</v>
+        <v>1.666501248109853e-06</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0001441746426280588</v>
+        <v>1.679826482359204e-07</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.813095877878368e-05</v>
+        <v>1.801201676698838e-07</v>
       </c>
       <c r="AE9" t="n">
-        <v>9.937054710462689e-05</v>
+        <v>2.139785920007853e-06</v>
       </c>
       <c r="AF9" t="n">
-        <v>6.070603194530122e-05</v>
+        <v>1.874179702099354e-06</v>
       </c>
       <c r="AG9" t="n">
-        <v>5.553246955969371e-05</v>
+        <v>1.961207090062089e-06</v>
       </c>
       <c r="AH9" t="n">
-        <v>5.011488974560052e-05</v>
+        <v>3.803770027843711e-07</v>
       </c>
       <c r="AI9" t="n">
-        <v>6.951438263058662e-05</v>
+        <v>4.753524990519509e-06</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4.024465306429192e-05</v>
+        <v>1.498428218837944e-06</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0003018919960595667</v>
+        <v>7.092679084053088e-07</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0001816431031329557</v>
+        <v>1.90117475540319e-07</v>
       </c>
       <c r="AM9" t="n">
-        <v>3.401021604076959e-05</v>
+        <v>1.454897073926986e-07</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.0001500809448771179</v>
+        <v>3.587396406601329e-07</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.0001624881697352976</v>
+        <v>1.036801222653594e-06</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.00012848453479819</v>
+        <v>6.078618071114761e-07</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0001283932651858777</v>
+        <v>2.119687110280211e-07</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.588609666214325e-05</v>
+        <v>2.395747287664562e-06</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.0001367280056001619</v>
+        <v>3.810362727563188e-07</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.662845119833946e-05</v>
+        <v>1.187052134810074e-06</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.001121829729527235</v>
+        <v>7.045618986012414e-06</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.0001618846436031163</v>
+        <v>9.731909358379198e-07</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.812497981125489e-05</v>
+        <v>9.906088962452486e-07</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.229076436487958e-05</v>
+        <v>3.979099801654229e-06</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.0001172524498542771</v>
+        <v>6.843269147793762e-06</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0004197589005343616</v>
+        <v>4.955153372065979e-07</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.0001679434790275991</v>
+        <v>2.002920837185229e-06</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.0001625605946173891</v>
+        <v>6.427679863918456e-07</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.578893665689975e-05</v>
+        <v>6.186841119415476e-07</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0002903149579651654</v>
+        <v>1.137914978244225e-06</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0002992796071339399</v>
+        <v>1.311314008489717e-06</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.877493721432984e-05</v>
+        <v>2.303259634572896e-06</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.000282326975138858</v>
+        <v>1.731100155666354e-06</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.0002185789489885792</v>
+        <v>1.686076274154402e-07</v>
       </c>
       <c r="BI9" t="n">
-        <v>5.221756873652339e-05</v>
+        <v>7.477868848582148e-07</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0002228934463346377</v>
+        <v>4.259712113707792e-06</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.0003162974899169058</v>
+        <v>4.206711423648812e-08</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0001090959849534556</v>
+        <v>7.330048390485899e-08</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0001654686639085412</v>
+        <v>2.32239881370333e-06</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.707854895968921e-05</v>
+        <v>7.285259471245809e-07</v>
       </c>
       <c r="BO9" t="n">
-        <v>8.407361747231334e-05</v>
+        <v>1.977221018023556e-06</v>
       </c>
       <c r="BP9" t="n">
-        <v>8.476828952552751e-05</v>
+        <v>1.441351173525618e-06</v>
       </c>
       <c r="BQ9" t="n">
-        <v>2.976757787109818e-05</v>
+        <v>8.206473012251081e-07</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.0001225361338583753</v>
+        <v>1.970964149222709e-06</v>
       </c>
       <c r="BS9" t="n">
-        <v>2.372489143454004e-05</v>
+        <v>1.100851250157575e-06</v>
       </c>
       <c r="BT9" t="n">
-        <v>8.294339932035655e-05</v>
+        <v>1.889286750156316e-06</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.47357417922467e-05</v>
+        <v>2.328087873593176e-07</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.0006513716070912778</v>
+        <v>3.262189466113341e-06</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0001497179036960006</v>
+        <v>7.506096153520048e-07</v>
       </c>
       <c r="BX9" t="n">
-        <v>8.579660061514005e-05</v>
+        <v>1.223093363478256e-06</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.057842594804242e-05</v>
+        <v>1.550179490550363e-06</v>
       </c>
       <c r="BZ9" t="n">
-        <v>8.509851795679424e-06</v>
+        <v>3.292037717983476e-06</v>
       </c>
       <c r="CA9" t="n">
-        <v>5.072478234069422e-05</v>
+        <v>5.93773108903406e-07</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.524679414113052e-06</v>
+        <v>1.619275508346618e-06</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.377466029836796e-05</v>
+        <v>3.921083191471553e-08</v>
       </c>
       <c r="CD9" t="n">
-        <v>8.167060877894983e-05</v>
+        <v>6.817296593908395e-08</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.0003189050767105073</v>
+        <v>1.539155846330686e-06</v>
       </c>
       <c r="CF9" t="n">
-        <v>6.631863652728498e-05</v>
+        <v>3.818142886302667e-07</v>
       </c>
       <c r="CG9" t="n">
-        <v>4.623439235729165e-05</v>
+        <v>9.637009270591079e-07</v>
       </c>
       <c r="CH9" t="n">
-        <v>6.810612831031904e-05</v>
+        <v>8.825053328109789e-07</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.166157835541526e-05</v>
+        <v>2.222833472842467e-06</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0001224772859131917</v>
+        <v>6.137962600405444e-07</v>
       </c>
       <c r="CK9" t="n">
-        <v>5.08287557750009e-05</v>
+        <v>3.518284188430698e-07</v>
       </c>
       <c r="CL9" t="n">
-        <v>8.686283399583772e-05</v>
+        <v>8.774790671850496e-07</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.0004538365465123206</v>
+        <v>5.230546662460256e-08</v>
       </c>
       <c r="CN9" t="n">
-        <v>6.880261935293674e-05</v>
+        <v>3.010694854310714e-06</v>
       </c>
       <c r="CO9" t="n">
-        <v>7.271065260283649e-05</v>
+        <v>2.52499125963368e-06</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0005464509013108909</v>
+        <v>4.111414909857558e-06</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.0003382407012395561</v>
+        <v>7.907331109890947e-07</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0004243392031639814</v>
+        <v>1.965241608559154e-06</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.0003089748206548393</v>
+        <v>5.525971573661081e-07</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.0001630076149012893</v>
+        <v>1.867475816652586e-06</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0002466056030243635</v>
+        <v>4.395261328227207e-07</v>
       </c>
       <c r="CV9" t="n">
-        <v>7.479024498024955e-05</v>
+        <v>2.268551355655291e-07</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.0003035457921214402</v>
+        <v>1.296880554946256e-06</v>
       </c>
       <c r="CX9" t="n">
-        <v>6.857843982288614e-05</v>
+        <v>4.113815634809725e-07</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0001324387994827703</v>
+        <v>1.352280833089026e-06</v>
       </c>
       <c r="CZ9" t="n">
-        <v>9.321765537606552e-05</v>
+        <v>9.975418606700259e-07</v>
       </c>
       <c r="DA9" t="n">
-        <v>3.159762491122819e-05</v>
+        <v>2.628138872751151e-06</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0001223819999722764</v>
+        <v>1.381135206202089e-09</v>
       </c>
       <c r="DC9" t="n">
-        <v>9.424450399819762e-05</v>
+        <v>2.94321893079541e-07</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0001018870752886869</v>
+        <v>5.485295559992664e-07</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.0001602504344191402</v>
+        <v>3.065380838052079e-07</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.0002697846502996981</v>
+        <v>2.980675617436646e-06</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.0001060251670423895</v>
+        <v>1.428810946890735e-06</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.0002537966065574437</v>
+        <v>9.656830002313654e-08</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.0005414252518676221</v>
+        <v>1.950915248016827e-06</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0007134765619412065</v>
+        <v>2.240873754999484e-06</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.012119411025196e-05</v>
+        <v>8.315998911712086e-07</v>
       </c>
       <c r="DL9" t="n">
-        <v>9.285258420277387e-05</v>
+        <v>4.079189466210664e-07</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0004017963947262615</v>
+        <v>8.594325890953769e-07</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.0001132622419390827</v>
+        <v>4.153641555149079e-07</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0001103864924516529</v>
+        <v>2.482081811194803e-07</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0001525800325907767</v>
+        <v>5.82933012083231e-07</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0001601546246092767</v>
+        <v>5.600585382126155e-07</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.784319313941523e-05</v>
+        <v>3.761632569876383e-07</v>
       </c>
       <c r="DS9" t="n">
-        <v>8.210854139178991e-05</v>
+        <v>1.434299576885678e-07</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.0002380119840381667</v>
+        <v>1.502299028288689e-06</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.0001968070573639125</v>
+        <v>2.710315811782493e-06</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.0001036545509123243</v>
+        <v>4.086997762442479e-07</v>
       </c>
       <c r="DW9" t="n">
-        <v>4.389646710478701e-05</v>
+        <v>4.012409817732987e-07</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0002336534962523729</v>
+        <v>5.699266125702707e-07</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.561427289852872e-05</v>
+        <v>7.213426442831405e-07</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0002411552704870701</v>
+        <v>2.286475819346379e-06</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.000179271912202239</v>
+        <v>1.259161081179627e-06</v>
       </c>
       <c r="EB9" t="n">
-        <v>6.672294693998992e-05</v>
+        <v>1.215090833284194e-06</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.868046042043716e-05</v>
+        <v>6.004449915053556e-08</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0001862592907855287</v>
+        <v>1.30082480609417e-06</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0003856640250887722</v>
+        <v>2.496816705388483e-06</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.0002549297641962767</v>
+        <v>1.703787262385958e-07</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0004440037009771913</v>
+        <v>7.792694418640167e-07</v>
       </c>
       <c r="EH9" t="n">
-        <v>2.573709934949875e-05</v>
+        <v>7.194722684289445e-07</v>
       </c>
       <c r="EI9" t="n">
-        <v>1.034650631481782e-05</v>
+        <v>5.608408741863968e-07</v>
       </c>
       <c r="EJ9" t="n">
-        <v>4.685897238232428e-06</v>
+        <v>9.080452514353965e-07</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0002432379842502996</v>
+        <v>1.606322939551319e-06</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.000168841754202731</v>
+        <v>5.279367201183049e-07</v>
       </c>
       <c r="EM9" t="n">
-        <v>9.037042764248326e-05</v>
+        <v>3.415898675029894e-07</v>
       </c>
       <c r="EN9" t="n">
-        <v>2.785430297080893e-05</v>
+        <v>1.324608405184335e-07</v>
       </c>
       <c r="EO9" t="n">
-        <v>8.689709648024291e-05</v>
+        <v>4.805992261935899e-07</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0001167322843684815</v>
+        <v>2.043582526312093e-06</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0001265308383153751</v>
+        <v>1.157423412223579e-06</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0001812790287658572</v>
+        <v>6.484280561380729e-07</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0001911258441396058</v>
+        <v>2.65766459506267e-07</v>
       </c>
       <c r="ET9" t="n">
-        <v>1.449551928089932e-05</v>
+        <v>1.72747377291671e-06</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.000333867414155975</v>
+        <v>9.894220056594349e-07</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0002429642336210236</v>
+        <v>3.351842678966932e-07</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0001060033100657165</v>
+        <v>6.103690566305886e-07</v>
       </c>
       <c r="EX9" t="n">
-        <v>9.93850699160248e-05</v>
+        <v>2.63361073393753e-07</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0003124684153590351</v>
+        <v>2.125008450093446e-06</v>
       </c>
       <c r="EZ9" t="n">
-        <v>5.056027293903753e-05</v>
+        <v>1.711809005655596e-07</v>
       </c>
       <c r="FA9" t="n">
-        <v>2.398886499577202e-05</v>
+        <v>1.616353529243497e-06</v>
       </c>
       <c r="FB9" t="n">
-        <v>6.406837928807363e-05</v>
+        <v>7.178064151958097e-07</v>
       </c>
       <c r="FC9" t="n">
-        <v>9.515457350062206e-06</v>
+        <v>2.286097696924116e-06</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0001864988298621029</v>
+        <v>5.653748758049915e-07</v>
       </c>
       <c r="FE9" t="n">
-        <v>7.94623265392147e-05</v>
+        <v>1.38033925622949e-07</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.0001460718340240419</v>
+        <v>1.819516910472885e-07</v>
       </c>
       <c r="FG9" t="n">
-        <v>9.368343307869509e-05</v>
+        <v>1.619992673340676e-07</v>
       </c>
       <c r="FH9" t="n">
-        <v>9.774856880540028e-05</v>
+        <v>1.995362936213496e-06</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.0001715690596029162</v>
+        <v>1.335662318524555e-06</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0002771826984826475</v>
+        <v>1.018633497551491e-06</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0001200075348606333</v>
+        <v>2.397688149358146e-06</v>
       </c>
       <c r="FL9" t="n">
-        <v>3.753237979253754e-05</v>
+        <v>2.278970214319997e-06</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.0001360860042041168</v>
+        <v>1.277662249776768e-06</v>
       </c>
       <c r="FN9" t="n">
-        <v>7.71599734434858e-05</v>
+        <v>1.766970285643765e-06</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0001498602796345949</v>
+        <v>2.901727384596597e-06</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.0002710186818148941</v>
+        <v>5.705722969651106e-07</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0001263443264178932</v>
+        <v>5.009051733395609e-07</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.0002092294016620144</v>
+        <v>2.896080559366965e-06</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.0002723265788517892</v>
+        <v>1.40922225000395e-06</v>
       </c>
       <c r="FT9" t="n">
-        <v>3.111476326012053e-05</v>
+        <v>3.967805696447613e-06</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.0002428536681691185</v>
+        <v>6.030808208379312e-08</v>
       </c>
       <c r="FV9" t="n">
-        <v>7.982909301063046e-05</v>
+        <v>1.474039947879646e-07</v>
       </c>
       <c r="FW9" t="n">
-        <v>8.873403203324415e-07</v>
+        <v>4.079403879586607e-06</v>
       </c>
       <c r="FX9" t="n">
-        <v>8.96219426067546e-05</v>
+        <v>1.870885739663208e-07</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.0003071661340072751</v>
+        <v>6.232333475963969e-07</v>
       </c>
       <c r="FZ9" t="n">
-        <v>8.165003237081692e-05</v>
+        <v>1.641509925320861e-06</v>
       </c>
       <c r="GA9" t="n">
-        <v>6.751508772140369e-05</v>
+        <v>2.432717565170606e-06</v>
       </c>
       <c r="GB9" t="n">
-        <v>1.665238960413262e-05</v>
+        <v>6.315553946478758e-08</v>
       </c>
       <c r="GC9" t="n">
-        <v>9.690553997643292e-05</v>
+        <v>3.058127049371251e-06</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.0001629586913622916</v>
+        <v>2.686270363483345e-06</v>
       </c>
       <c r="GE9" t="n">
-        <v>1.806791988201439e-05</v>
+        <v>2.506860141693323e-07</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.0001598936360096559</v>
+        <v>6.981475735301501e-07</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.0001296707923756912</v>
+        <v>7.436117925863073e-07</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.00167021865490824</v>
+        <v>0.0002845706476364285</v>
       </c>
       <c r="B10" t="n">
-        <v>9.457235137233511e-05</v>
+        <v>4.116450145374984e-05</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0001039326598402113</v>
+        <v>0.0003513158881105483</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0004113095346838236</v>
+        <v>4.370500391814858e-06</v>
       </c>
       <c r="E10" t="n">
-        <v>8.604559843661264e-05</v>
+        <v>0.0002429278974886984</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001741273095831275</v>
+        <v>0.0001889189588837326</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0002676239528227597</v>
+        <v>0.0001904700766317546</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0008560880087316036</v>
+        <v>9.807941387407482e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>3.276838469901122e-05</v>
+        <v>5.51759876543656e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001234577037394047</v>
+        <v>0.0002218269655713812</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0001699691492831334</v>
+        <v>0.0001012149587040767</v>
       </c>
       <c r="L10" t="n">
-        <v>2.443724952172488e-05</v>
+        <v>0.000335507036652416</v>
       </c>
       <c r="M10" t="n">
-        <v>0.000219470530282706</v>
+        <v>4.957719647791237e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.000489481317345053</v>
+        <v>0.0002134509268216789</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001377980457618833</v>
+        <v>0.0003517789882607758</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0006541566690430045</v>
+        <v>0.0001557462674099952</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.000984865939244628</v>
+        <v>7.422069029416889e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001051660001394339</v>
+        <v>6.483511242549866e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0001898791088024154</v>
+        <v>9.546357614453882e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0005104299052618444</v>
+        <v>0.0002309273986611515</v>
       </c>
       <c r="U10" t="n">
-        <v>3.203335654688999e-05</v>
+        <v>0.0001406455994583666</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0004628211027011275</v>
+        <v>0.0001050041464623064</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0006969345267862082</v>
+        <v>0.0001612154010217637</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0003153313009534031</v>
+        <v>0.0001811901020118967</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0003236066550016403</v>
+        <v>6.176505848998204e-05</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0001597583468537778</v>
+        <v>2.815273910528049e-05</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.049503958318383e-05</v>
+        <v>2.70626405836083e-05</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0003404128656256944</v>
+        <v>5.058411989011802e-05</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.0003432836092542857</v>
+        <v>9.519295417703688e-05</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0001445720554329455</v>
+        <v>2.093514922307804e-06</v>
       </c>
       <c r="AE10" t="n">
-        <v>9.105939534492791e-05</v>
+        <v>4.054516466567293e-06</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.436747697880492e-05</v>
+        <v>5.25549694430083e-07</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0002059012185782194</v>
+        <v>4.096018892596476e-05</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.703036105027422e-05</v>
+        <v>8.404911932302639e-05</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0002679356839507818</v>
+        <v>2.126984327333048e-05</v>
       </c>
       <c r="AJ10" t="n">
-        <v>4.354572593001649e-05</v>
+        <v>4.749907020595856e-05</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0003242402744945139</v>
+        <v>1.497523044236004e-05</v>
       </c>
       <c r="AL10" t="n">
-        <v>6.94378322805278e-05</v>
+        <v>0.0001532843452878296</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.000275331549346447</v>
+        <v>6.919736188137904e-05</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.000114569251309149</v>
+        <v>6.246727571124211e-05</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.0001353005063720047</v>
+        <v>5.806615081382915e-05</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.333595668664202e-05</v>
+        <v>2.330707502551377e-05</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0001418007013853639</v>
+        <v>7.192896009655669e-05</v>
       </c>
       <c r="AR10" t="n">
-        <v>7.619181269546971e-05</v>
+        <v>5.161129956832156e-05</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.997238905460108e-05</v>
+        <v>4.475112655200064e-05</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.0009070850792340934</v>
+        <v>2.136469083779957e-05</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.000221832815441303</v>
+        <v>3.331449261168018e-05</v>
       </c>
       <c r="AV10" t="n">
-        <v>8.402916137129068e-06</v>
+        <v>0.0001664221053943038</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0004851377452723682</v>
+        <v>7.248120527947322e-05</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.001159089268185198</v>
+        <v>7.020934572210535e-05</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.0007836536387912929</v>
+        <v>0.0001953776954906061</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.000214110070373863</v>
+        <v>5.746536407968961e-05</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0004195109358988702</v>
+        <v>0.0001765969209372997</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.156238719588146e-05</v>
+        <v>6.356993981171399e-05</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.000372301583411172</v>
+        <v>0.0002097870601573959</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0001624443248147145</v>
+        <v>7.369628292508423e-05</v>
       </c>
       <c r="BE10" t="n">
-        <v>9.064738696906716e-05</v>
+        <v>4.100907972315326e-06</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.000129853084217757</v>
+        <v>2.306440728716552e-05</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.0003903942997567356</v>
+        <v>6.98645890224725e-05</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.0003902594035025686</v>
+        <v>9.912991663441062e-05</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.0003353790671098977</v>
+        <v>7.871654815971851e-05</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.0004055915051139891</v>
+        <v>0.000183473268407397</v>
       </c>
       <c r="BK10" t="n">
-        <v>3.783356805797666e-05</v>
+        <v>1.36747785290936e-05</v>
       </c>
       <c r="BL10" t="n">
-        <v>2.205625605711248e-05</v>
+        <v>0.0001067290431819856</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.0002696837473195046</v>
+        <v>8.782050281297415e-05</v>
       </c>
       <c r="BN10" t="n">
-        <v>9.568194218445569e-05</v>
+        <v>0.0001613433560123667</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0004294213431421667</v>
+        <v>0.0001256528194062412</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0003837457334157079</v>
+        <v>0.0001683606387814507</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.100034857401624e-05</v>
+        <v>1.770026574376971e-05</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0003631241852417588</v>
+        <v>1.418005194864236e-05</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.0004840173642151058</v>
+        <v>5.979699926683679e-05</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.000231667043408379</v>
+        <v>2.733158544288017e-05</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.0004505117249209434</v>
+        <v>3.774874494411051e-05</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.000261965295067057</v>
+        <v>0.000199053916730918</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.000180715651367791</v>
+        <v>0.0001503590756328776</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0002590147196315229</v>
+        <v>7.558496145065874e-05</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.0005098658730275929</v>
+        <v>0.0001156370781245641</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.000585670059081167</v>
+        <v>0.000233451573876664</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.707853804575279e-05</v>
+        <v>7.526332410634495e-06</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.0001970465818885714</v>
+        <v>2.223123556177597e-05</v>
       </c>
       <c r="CC10" t="n">
-        <v>1.544131737318821e-05</v>
+        <v>3.954645217163488e-05</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0003249882720410824</v>
+        <v>6.48438508505933e-05</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.0002376708289375529</v>
+        <v>0.0001357399742119014</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.394972034380771e-05</v>
+        <v>7.506688416469842e-05</v>
       </c>
       <c r="CG10" t="n">
-        <v>1.570706444908865e-05</v>
+        <v>8.179075666703284e-05</v>
       </c>
       <c r="CH10" t="n">
-        <v>3.818058030446991e-05</v>
+        <v>5.263241473585367e-05</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.0002575337130110711</v>
+        <v>5.190487354411744e-05</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.672460686881095e-05</v>
+        <v>4.671094757213723e-06</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.0003021221491508186</v>
+        <v>3.474405821179971e-05</v>
       </c>
       <c r="CL10" t="n">
-        <v>3.335371002322063e-05</v>
+        <v>2.136584225809202e-05</v>
       </c>
       <c r="CM10" t="n">
-        <v>3.04564819089137e-05</v>
+        <v>2.517998109397013e-05</v>
       </c>
       <c r="CN10" t="n">
-        <v>8.544472802896053e-05</v>
+        <v>6.703023245790973e-05</v>
       </c>
       <c r="CO10" t="n">
-        <v>5.306265666149557e-05</v>
+        <v>7.228417962323874e-05</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.838301043084357e-05</v>
+        <v>4.121501842746511e-05</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.0007699021953158081</v>
+        <v>6.838799163233489e-05</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.0001226038439199328</v>
+        <v>3.489452501526102e-05</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.0002251061087008566</v>
+        <v>0.0001264276797883213</v>
       </c>
       <c r="CT10" t="n">
-        <v>6.472003587987274e-05</v>
+        <v>4.855604493059218e-05</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.0001393267011735588</v>
+        <v>1.282876110053621e-05</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0002993880480062217</v>
+        <v>6.743473204551265e-05</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.0002217972651124001</v>
+        <v>9.504622721578926e-05</v>
       </c>
       <c r="CX10" t="n">
-        <v>4.503293166635558e-05</v>
+        <v>6.342241249512881e-05</v>
       </c>
       <c r="CY10" t="n">
-        <v>9.8626253020484e-05</v>
+        <v>7.703118171775714e-05</v>
       </c>
       <c r="CZ10" t="n">
-        <v>3.361049311934039e-05</v>
+        <v>4.523683310253546e-05</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.0002509529876988381</v>
+        <v>5.475396028487012e-05</v>
       </c>
       <c r="DB10" t="n">
-        <v>9.168230462819338e-06</v>
+        <v>2.578637941041961e-05</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.000317820260534063</v>
+        <v>1.031508782034507e-05</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.331703944946639e-05</v>
+        <v>9.382628377352376e-06</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.0001015603847918101</v>
+        <v>8.372783486265689e-05</v>
       </c>
       <c r="DF10" t="n">
-        <v>4.186153091723099e-06</v>
+        <v>2.029938332270831e-05</v>
       </c>
       <c r="DG10" t="n">
-        <v>8.462984260404482e-05</v>
+        <v>8.753647853154689e-05</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.0002712910354603082</v>
+        <v>9.287933062296361e-05</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.001021156320348382</v>
+        <v>0.0001209652400575578</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0001048705671564676</v>
+        <v>6.690370355499908e-05</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.082425923319533e-05</v>
+        <v>3.196422039764002e-05</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.0004910093848593533</v>
+        <v>3.395717430976219e-05</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.0003435872786212713</v>
+        <v>1.992621764657088e-05</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.0001932077575474977</v>
+        <v>3.052259125979617e-05</v>
       </c>
       <c r="DO10" t="n">
-        <v>9.108742233365774e-05</v>
+        <v>5.519985643331893e-05</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.0001477284531574696</v>
+        <v>0.0001550452725496143</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.0002956194803118706</v>
+        <v>0.0001169196766568348</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.0002545712632127106</v>
+        <v>4.054810415254906e-05</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.0002335230819880962</v>
+        <v>0.0001163043634733185</v>
       </c>
       <c r="DT10" t="n">
-        <v>1.033703301800415e-05</v>
+        <v>4.192177584627643e-05</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.0004397512238938361</v>
+        <v>7.888139407441486e-06</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.0001359848247375339</v>
+        <v>7.391051894956036e-06</v>
       </c>
       <c r="DW10" t="n">
-        <v>2.156382834073156e-06</v>
+        <v>4.963086030329578e-05</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.000174379616510123</v>
+        <v>4.447580795385875e-05</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.831164450384676e-06</v>
+        <v>0.0002256112347822636</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.0001053648957167752</v>
+        <v>0.0001201660998049192</v>
       </c>
       <c r="EA10" t="n">
-        <v>6.966355431359261e-05</v>
+        <v>2.728130129980855e-05</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.0004054703167639673</v>
+        <v>0.0001241442805621773</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.0002119124983437359</v>
+        <v>2.072961251542438e-05</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.000367523287422955</v>
+        <v>2.55653740168782e-05</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.0001539886288810521</v>
+        <v>1.925789547385648e-06</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.0002663191989995539</v>
+        <v>3.364745498402044e-05</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.0004039595078211278</v>
+        <v>0.0001899069757200778</v>
       </c>
       <c r="EH10" t="n">
-        <v>1.525594143458875e-05</v>
+        <v>1.849455293267965e-05</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0001829966640798375</v>
+        <v>5.304724982124753e-05</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.0001377759617753327</v>
+        <v>0.0001031080755637959</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.0001358421868644655</v>
+        <v>6.546754775627051e-06</v>
       </c>
       <c r="EL10" t="n">
-        <v>4.225572774885222e-05</v>
+        <v>2.999361277034041e-05</v>
       </c>
       <c r="EM10" t="n">
-        <v>1.93957475858042e-05</v>
+        <v>4.254993109498173e-05</v>
       </c>
       <c r="EN10" t="n">
-        <v>6.253326864680275e-05</v>
+        <v>3.496760837151669e-05</v>
       </c>
       <c r="EO10" t="n">
-        <v>9.829392365645617e-05</v>
+        <v>4.722438825410791e-05</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.0003070847596973181</v>
+        <v>0.0001221645652549341</v>
       </c>
       <c r="EQ10" t="n">
-        <v>7.616166840307415e-05</v>
+        <v>6.350100011331961e-05</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.000132653716718778</v>
+        <v>1.293811146751978e-05</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.0004557844949886203</v>
+        <v>3.061180905206129e-05</v>
       </c>
       <c r="ET10" t="n">
-        <v>8.481410623062402e-05</v>
+        <v>0.0001446355890948325</v>
       </c>
       <c r="EU10" t="n">
-        <v>2.369064895901829e-05</v>
+        <v>4.393735434859991e-05</v>
       </c>
       <c r="EV10" t="n">
-        <v>6.031319935573265e-05</v>
+        <v>0.0001642536517465487</v>
       </c>
       <c r="EW10" t="n">
-        <v>2.31600170081947e-05</v>
+        <v>4.494047607295215e-05</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0002573538513388485</v>
+        <v>5.405039701145142e-05</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.0001832035486586392</v>
+        <v>9.381685958942398e-05</v>
       </c>
       <c r="EZ10" t="n">
-        <v>4.149982851231471e-05</v>
+        <v>5.841600795974955e-05</v>
       </c>
       <c r="FA10" t="n">
-        <v>7.206894224509597e-05</v>
+        <v>9.20398160815239e-05</v>
       </c>
       <c r="FB10" t="n">
-        <v>7.042604556772858e-05</v>
+        <v>6.559869507327676e-05</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.0002192361571360379</v>
+        <v>8.444026752840728e-05</v>
       </c>
       <c r="FD10" t="n">
-        <v>5.375863838708028e-05</v>
+        <v>1.181417610496283e-05</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.0004133410402573645</v>
+        <v>4.956786142429337e-06</v>
       </c>
       <c r="FF10" t="n">
-        <v>5.782567313872278e-07</v>
+        <v>3.482586180325598e-06</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.0001954740146175027</v>
+        <v>0.0001010437117656693</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.0002578626153990626</v>
+        <v>5.009950837120414e-05</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.000141154756420292</v>
+        <v>3.099008608842269e-05</v>
       </c>
       <c r="FJ10" t="n">
-        <v>6.83922553434968e-05</v>
+        <v>6.718456279486418e-05</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.0001891303836600855</v>
+        <v>0.000169078863109462</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.0002186479250667617</v>
+        <v>0.0001702331937849522</v>
       </c>
       <c r="FM10" t="n">
-        <v>5.577541378443129e-05</v>
+        <v>5.207703361520544e-05</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.0001239460834767669</v>
+        <v>0.000123813355457969</v>
       </c>
       <c r="FO10" t="n">
-        <v>6.068305083317682e-06</v>
+        <v>5.254218922345899e-05</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.0001530023582745343</v>
+        <v>3.392765938770026e-05</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.00013038631004747</v>
+        <v>0.0002019608800765127</v>
       </c>
       <c r="FR10" t="n">
-        <v>1.128824078477919e-05</v>
+        <v>0.0002510814229026437</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.0004744056495837867</v>
+        <v>2.407183637842536e-05</v>
       </c>
       <c r="FT10" t="n">
-        <v>2.861343455151655e-05</v>
+        <v>0.0003400120476726443</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.0004335285630077124</v>
+        <v>5.441458051791415e-05</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.000273186044069007</v>
+        <v>0.0002336479956284165</v>
       </c>
       <c r="FW10" t="n">
-        <v>5.068710379418917e-05</v>
+        <v>8.208354120142758e-05</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.0001207228560815565</v>
+        <v>0.00012780494580511</v>
       </c>
       <c r="FY10" t="n">
-        <v>7.045459642540663e-05</v>
+        <v>3.680904046632349e-05</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.0002105933090206236</v>
+        <v>5.894929927308112e-05</v>
       </c>
       <c r="GA10" t="n">
-        <v>2.326890535186976e-05</v>
+        <v>0.0001227341126650572</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.0001587430451763794</v>
+        <v>4.456578244571574e-05</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.0001496007316745818</v>
+        <v>3.791035123867914e-05</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.0003080392198171467</v>
+        <v>5.053302811575122e-05</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.0002867106813937426</v>
+        <v>4.514684769674204e-05</v>
       </c>
       <c r="GF10" t="n">
-        <v>4.808702215086669e-06</v>
+        <v>0.0002294382429681718</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.0001312531239818782</v>
+        <v>6.806275632698089e-05</v>
       </c>
     </row>
   </sheetData>
